--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_50_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_50_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="31">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>81.2</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>18.44</v>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>0.36</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>19.2665</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>19.1972</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>99.64</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>0.0693</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>0.36</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2123,11 +2123,11 @@
       </c>
       <c r="B27" s="22">
         <f>SUM(B25:B26)</f>
-        <v/>
+        <v>19.2715</v>
       </c>
       <c r="C27" s="23">
         <f>SUM(C25:C26)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D27" s="17" t="inlineStr"/>
       <c r="E27" s="17" t="inlineStr"/>
@@ -2246,6 +2246,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2485,6 +2486,7 @@
       <c r="F16" s="17" t="inlineStr"/>
       <c r="G16" s="17" t="inlineStr"/>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
@@ -2531,6 +2533,7 @@
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="108" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
         <is>
@@ -2853,11 +2856,11 @@
       </c>
       <c r="B15" s="33">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>148.43</v>
       </c>
       <c r="C15" s="23">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -2867,19 +2870,19 @@
       <c r="E15" s="17" t="inlineStr"/>
       <c r="F15" s="17">
         <f>ROUND(AVERAGE(F10:F14),2)</f>
-        <v/>
+        <v>28.14</v>
       </c>
       <c r="G15" s="22">
         <f>ROUND(AVERAGE(G10:G14),4)</f>
-        <v/>
+        <v>0.667</v>
       </c>
       <c r="H15" s="23">
         <f>ROUND(AVERAGE(H10:H14),2)</f>
-        <v/>
+        <v>94.61</v>
       </c>
       <c r="I15" s="23">
         <f>ROUND(AVERAGE(I10:I14),2)</f>
-        <v/>
+        <v>5.51</v>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
